--- a/reports/越南猪肉零售价格日报_2026-07-23.xlsx
+++ b/reports/越南猪肉零售价格日报_2026-07-23.xlsx
@@ -554,7 +554,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>采集时间：越南时间 07:58。所有商品售价均统一折算为 VND/kg；常规价和促销价分别保留。</t>
+          <t>采集时间：越南时间 08:15。所有商品售价均统一折算为 VND/kg；常规价和促销价分别保留。</t>
         </is>
       </c>
     </row>
